--- a/cypress/downloads/BAS_Stock_Template.xlsx
+++ b/cypress/downloads/BAS_Stock_Template.xlsx
@@ -38,10 +38,10 @@
     <x:t>Quantity*</x:t>
   </x:si>
   <x:si>
-    <x:t>Vendor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MinimumStockThreshold</x:t>
+    <x:t>Vendor*</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MinimumStockThreshold*</x:t>
   </x:si>
   <x:si>
     <x:t>BulkSellingPrice</x:t>
@@ -612,7 +612,7 @@
     <x:col min="6" max="6" width="10.282054" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="9.853482" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="14.139196" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="23.853482" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="14.853482" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="13.282054" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="12.853482" style="0" customWidth="1"/>

--- a/cypress/downloads/BAS_Stock_Template.xlsx
+++ b/cypress/downloads/BAS_Stock_Template.xlsx
@@ -252,7 +252,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
-      <x:color rgb="FF000000"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -266,7 +266,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
+        <x:fgColor rgb="FF0F766E"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
